--- a/data/trans_orig/IP3104-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3104-Edad-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33655</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44851</t>
+          <t>44592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>59977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77572</t>
+          <t>78537</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37899</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139752</t>
+          <t>139009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164737</t>
+          <t>165043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135854</t>
+          <t>135230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162426</t>
+          <t>159728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>283944</t>
+          <t>283878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318089</t>
+          <t>317912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48024</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68631</t>
+          <t>68662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56661</t>
+          <t>55818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79114</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109549</t>
+          <t>109917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140232</t>
+          <t>139710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>49670</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>49185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66998</t>
+          <t>67371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55983</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>76853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112476</t>
+          <t>113529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138160</t>
+          <t>139406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34695</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51922</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52459</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73795</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98142</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>46506</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>11734</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>24264</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>96116</t>
+          <t>95883</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>118020</t>
+          <t>117978</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99020</t>
+          <t>100727</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>122647</t>
+          <t>122683</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>202486</t>
+          <t>199766</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>234390</t>
+          <t>234262</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>46107</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>66742</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51199</t>
+          <t>51117</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102404</t>
+          <t>101815</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129693</t>
+          <t>132464</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23563</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28954</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48130</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>45939</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58854</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>68788</t>
+          <t>68835</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>328696</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>367802</t>
+          <t>368966</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>343885</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>384464</t>
+          <t>384362</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>684148</t>
+          <t>685820</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>740291</t>
+          <t>743700</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>153156</t>
+          <t>155419</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>190480</t>
+          <t>192224</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>166485</t>
+          <t>165616</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>204762</t>
+          <t>202131</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333590</t>
+          <t>329670</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>383358</t>
+          <t>383276</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74737</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>74259</t>
+          <t>74403</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>106688</t>
+          <t>106302</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>139986</t>
+          <t>139851</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,49 +4493,49 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>13535</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>8418</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>20404</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>13535</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>38</t>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>33589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43897</t>
+          <t>43756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58827</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38732</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53432</t>
+          <t>54156</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>85390</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107584</t>
+          <t>107605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26987</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>46598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103045</t>
+          <t>103237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129950</t>
+          <t>129071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137814</t>
+          <t>136609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164077</t>
+          <t>164761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248271</t>
+          <t>250699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286226</t>
+          <t>288034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>57732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>79912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59858</t>
+          <t>59579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85102</t>
+          <t>83105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123797</t>
+          <t>122032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156770</t>
+          <t>157343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34054</t>
+          <t>33862</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>54438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70342</t>
+          <t>70973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90682</t>
+          <t>91226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60697</t>
+          <t>61480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81277</t>
+          <t>81035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>137092</t>
+          <t>137100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165102</t>
+          <t>167956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39084</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57740</t>
+          <t>57878</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70683</t>
+          <t>69638</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96344</t>
+          <t>94495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>123503</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6997,82 +6997,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12296</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7882</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>19331</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>28253</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>20979</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>37835</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>12296</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>7786</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>19651</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>28253</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>20610</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>37933</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22795</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -7551,12 +7551,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>69364</t>
+          <t>69665</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91473</t>
+          <t>91168</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>66454</t>
+          <t>65559</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87232</t>
+          <t>86482</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>141712</t>
+          <t>143051</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>172704</t>
+          <t>173142</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49531</t>
+          <t>50926</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70173</t>
+          <t>70479</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49399</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69783</t>
+          <t>69882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>104487</t>
+          <t>105097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134002</t>
+          <t>132725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22840</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>49146</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>24818</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>37564</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>59614</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>94918</t>
+          <t>94797</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>309157</t>
+          <t>305178</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>350016</t>
+          <t>351202</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>324271</t>
+          <t>322471</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>367235</t>
+          <t>366465</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>644650</t>
+          <t>642111</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>704645</t>
+          <t>703335</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>175899</t>
+          <t>176653</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>214555</t>
+          <t>215166</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>189191</t>
+          <t>188574</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>227800</t>
+          <t>228026</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>377210</t>
+          <t>374854</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>431317</t>
+          <t>432693</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>46824</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70271</t>
+          <t>70924</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>46730</t>
+          <t>46945</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>99721</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>133643</t>
+          <t>132453</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>56892</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9260,12 +9260,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40211</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>65861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86193</t>
+          <t>85596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51321</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -9712,12 +9712,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65270</t>
+          <t>64216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>85746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95451</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121172</t>
+          <t>120954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164719</t>
+          <t>166216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200010</t>
+          <t>200251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84112</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71323</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96147</t>
+          <t>96855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10331,47 +10331,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>157550</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>140564</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>174152</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>33,79%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>37,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>157550</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>140893</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>173944</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>33,79%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>47739</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>51650</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>65610</t>
+          <t>66510</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91990</t>
+          <t>91648</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -10850,12 +10850,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10935,12 +10935,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>57136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78676</t>
+          <t>78577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>50172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70325</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>113470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144251</t>
+          <t>143347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56527</t>
+          <t>56021</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77986</t>
+          <t>78565</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62526</t>
+          <t>61898</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>83501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124305</t>
+          <t>125213</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>153979</t>
+          <t>156388</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41763</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>39058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50332</t>
+          <t>50839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73759</t>
+          <t>75639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -11302,12 +11302,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -11645,12 +11645,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -11758,12 +11758,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46604</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>67783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39441</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>59862</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>93319</t>
+          <t>92958</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>121318</t>
+          <t>122372</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>72395</t>
+          <t>73803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57297</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79723</t>
+          <t>80274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114422</t>
+          <t>116562</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>144725</t>
+          <t>147717</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -11984,12 +11984,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>45723</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>39267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>55069</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>80334</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12097,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25118</t>
+          <t>24834</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12490,12 +12490,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55396</t>
+          <t>54826</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>222684</t>
+          <t>221998</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>262668</t>
+          <t>261939</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>228509</t>
+          <t>227770</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>271195</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>465556</t>
+          <t>466295</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>524915</t>
+          <t>526996</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>202773</t>
+          <t>201642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>242683</t>
+          <t>242869</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>226649</t>
+          <t>226001</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>269096</t>
+          <t>267799</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>439239</t>
+          <t>442072</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>498004</t>
+          <t>499370</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>98586</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>128173</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>94350</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>200068</t>
+          <t>202340</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>244440</t>
+          <t>246259</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -12892,12 +12892,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78418</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>99564</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>130266</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -13354,12 +13354,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -13467,12 +13467,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13482,12 +13482,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26100</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13630,12 +13630,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49314</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13665,12 +13665,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -13693,12 +13693,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37107</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13856,12 +13856,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14004,12 +14004,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -14149,12 +14149,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14164,12 +14164,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -14262,12 +14262,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15595</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14277,12 +14277,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14312,12 +14312,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23961</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -14375,12 +14375,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>45480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65348</t>
+          <t>65052</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14410,12 +14410,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44765</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66255</t>
+          <t>66004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14425,12 +14425,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97012</t>
+          <t>95469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126292</t>
+          <t>125183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -14488,12 +14488,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48741</t>
+          <t>49897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70572</t>
+          <t>70560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>58447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81949</t>
+          <t>80666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14558,12 +14558,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112251</t>
+          <t>114117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143285</t>
+          <t>146267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -14601,12 +14601,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33084</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14616,12 +14616,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50967</t>
+          <t>50923</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56210</t>
+          <t>55428</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79537</t>
+          <t>80354</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14686,12 +14686,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -14714,12 +14714,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14729,12 +14729,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14764,12 +14764,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14799,12 +14799,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -14944,12 +14944,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -14959,12 +14959,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15014,12 +15014,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15029,12 +15029,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -15057,12 +15057,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15092,12 +15092,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15107,12 +15107,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15127,12 +15127,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15142,12 +15142,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15170,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58886</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15185,12 +15185,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56958</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84208</t>
+          <t>82844</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>101116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135345</t>
+          <t>134368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -15283,12 +15283,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47211</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>70076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15298,12 +15298,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74083</t>
+          <t>74255</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101857</t>
+          <t>101551</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128661</t>
+          <t>128132</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164016</t>
+          <t>164731</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>59122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>50571</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>72645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>103901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15481,12 +15481,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -15509,12 +15509,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15544,12 +15544,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15559,12 +15559,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15579,12 +15579,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -15739,12 +15739,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -15852,12 +15852,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15887,12 +15887,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15902,12 +15902,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15922,12 +15922,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15937,12 +15937,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -15965,12 +15965,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>71495</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123062</t>
+          <t>123389</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>82563</t>
+          <t>85609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>129896</t>
+          <t>131509</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16015,12 +16015,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16035,12 +16035,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>173720</t>
+          <t>175209</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>239153</t>
+          <t>239249</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -16078,12 +16078,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93179</t>
+          <t>91630</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83414</t>
+          <t>86367</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>121103</t>
+          <t>119771</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>147719</t>
+          <t>147538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>202894</t>
+          <t>202038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -16191,12 +16191,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131790</t>
+          <t>133077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16206,12 +16206,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55457</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>88507</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16241,12 +16241,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113973</t>
+          <t>115243</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>218149</t>
+          <t>216558</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16304,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16319,12 +16319,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16354,12 +16354,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33208</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -16534,12 +16534,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16569,12 +16569,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16604,12 +16604,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16619,12 +16619,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -16647,12 +16647,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16662,49 +16662,49 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>29782</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>21379</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>41972</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>29782</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>20977</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -16717,12 +16717,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>44293</t>
+          <t>43641</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>70621</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>194500</t>
+          <t>195085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>252684</t>
+          <t>253087</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16775,12 +16775,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>222523</t>
+          <t>223734</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>280782</t>
+          <t>278655</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>433500</t>
+          <t>437639</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>514304</t>
+          <t>523506</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>178436</t>
+          <t>178506</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>230152</t>
+          <t>230921</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16908,12 +16908,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>250983</t>
+          <t>250233</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>300081</t>
+          <t>301636</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16943,12 +16943,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>444499</t>
+          <t>445507</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>516073</t>
+          <t>521974</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -16986,12 +16986,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>120588</t>
+          <t>120837</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>228412</t>
+          <t>221461</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>136564</t>
+          <t>136757</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>178280</t>
+          <t>180842</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17056,12 +17056,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>271896</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>381281</t>
+          <t>373140</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17071,12 +17071,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -17099,12 +17099,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44384</t>
+          <t>44565</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70628</t>
+          <t>69726</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17184,12 +17184,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
